--- a/Processed_Data/pm10_conv_fact.xlsx
+++ b/Processed_Data/pm10_conv_fact.xlsx
@@ -821,7 +821,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Turkey</t>
+          <t>Türkiye</t>
         </is>
       </c>
       <c r="B41" t="n">
